--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.10.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.10.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.10.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.10.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="60" customWidth="1" min="15" max="15"/>
+    <col width="38" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -594,7 +594,7 @@
       <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>L1: localized OCR phrase divergence vs other OCR: "" vs "III INTRODUCTORY REMARKS" :: ï»¿III.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | localized OCR phrase divergence vs other OCR: "" vs "III INTRODUCTORY REMARKS" :: [BOM]III.</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
@@ -609,24 +609,28 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L15: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L15: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | localized OCR phrase divergence vs other OCR: "" vs "III INTRODUCTORY REMARKS" :: [BOM]III.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | localized OCR phrase divergence vs other OCR: "" vs "III INTRODUCTORY REMARKS" :: [BOM]III.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L15: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L15: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L5: isolated marker/symbol line :: —</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -638,7 +642,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L61: line starts with digit/letter garbage token | suspicious token(s): 1er (letter/digit mix) :: 1er and</t>
+          <t>L47: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • press,</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -661,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -670,28 +674,28 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L24: stray/suspicious non-ASCII glyph(s): U+00A2 CENT SIGN | isolated marker/symbol line :: â…¢</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L7: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: It may not be out of place,â€”but chiefly with a view to those</t>
+          <t>L47: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • press,</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L24: stray/suspicious non-ASCII glyph(s): U+00A2 CENT SIGN | isolated marker/symbol line :: â…¢</t>
+          <t>L24: isolated marker/symbol line :: Ⅲ</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr"/>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L60: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •public</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -721,14 +725,10 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: vs. ELDER.â€”Grant's Chancery Reports, Vol. 1.</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L9: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: to Equity,â€”to refer to a few of those cases, in which the proper relief</t>
+          <t>L60: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •public</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -742,7 +742,11 @@
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L61: line starts with digit/letter garbage token | suspicious token(s): 1er (letter/digit mix) :: 1er and</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr"/>
@@ -758,12 +762,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -773,11 +777,7 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L25: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: vs. ELDER.â€”Grantâ€™s Chancery Reports, Vol. 1.</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -820,11 +820,7 @@
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ press,</t>
-        </is>
-      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -867,11 +863,7 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢public</t>
-        </is>
-      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -977,12 +969,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1021,7 +1013,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1138,7 +1130,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
